--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -677,8 +677,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -688,13 +691,13 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -703,37 +706,34 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v/>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -772,7 +772,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
@@ -784,12 +784,12 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -825,8 +825,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4645
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -835,7 +838,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -875,7 +878,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -890,36 +893,38 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">77
+990
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -949,13 +954,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -976,13 +981,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1000,13 +1005,11 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>01400</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v/>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1016,13 +1019,13 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1033,13 +1036,13 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -1048,25 +1051,24 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
@@ -1094,19 +1096,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9310
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1127,7 +1129,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3552
 </t>
         </is>
       </c>
@@ -1151,56 +1153,57 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1212,7 +1215,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1224,13 +1227,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1242,25 +1245,25 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1281,7 +1284,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3279
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1299,66 +1302,64 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v/>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v/>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13189
+          <t xml:space="preserve">127219
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1376,13 +1377,13 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1400,7 +1401,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1436,7 +1437,8 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1452,47 +1454,51 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1342
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1507,13 +1513,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">8929
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
@@ -1539,7 +1545,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1551,7 +1557,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1569,31 +1575,31 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v/>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1603,13 +1609,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1628,65 +1634,67 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n">
-        <v/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16379
+</t>
+        </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">430
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">541
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1901
 </t>
         </is>
       </c>
@@ -1698,7 +1706,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1719,124 +1727,132 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">77871
+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
       </c>
       <c r="E11" s="3" t="n">
         <v/>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11975
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v/>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1855,13 +1871,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -1870,58 +1885,57 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>041</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
         <v/>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="J12" s="3" t="n">
+        <v/>
       </c>
       <c r="K12" s="3" t="n">
         <v/>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">277275
+163
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1933,19 +1947,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1963,25 +1977,24 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8850
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2002,19 +2015,20 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2025,62 +2039,59 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>447</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v/>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -2090,16 +2101,16 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">668
@@ -2108,7 +2119,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
@@ -2126,18 +2137,21 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2173,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2171,119 +2185,123 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3561
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9908
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9979
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2065
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -2307,13 +2325,13 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2325,13 +2343,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -2342,15 +2361,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
+          <t xml:space="preserve">3252
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v/>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2359,15 +2375,18 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v/>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184883
+</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9226
 </t>
         </is>
       </c>
@@ -2376,7 +2395,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2394,13 +2413,13 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2411,12 +2430,12 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2447,18 +2466,18 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2470,25 +2489,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">4236
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4819
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2500,83 +2519,84 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v/>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">9416
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2599,7 +2619,8 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t xml:space="preserve">2579
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2610,8 +2631,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2622,13 +2642,13 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">4891
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2638,40 +2658,33 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
+          <t xml:space="preserve">4381
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v/>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2681,30 +2694,29 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
-</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2716,7 +2728,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11909
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2728,7 +2740,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2758,30 +2770,31 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">98
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2793,7 +2806,8 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
@@ -2807,76 +2821,74 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>124</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7420
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v/>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>6340880</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2894,55 +2906,65 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>214251</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v/>
       </c>
       <c r="N19" s="3" t="n">
         <v/>
@@ -2950,15 +2972,12 @@
       <c r="O19" s="3" t="n">
         <v/>
       </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
+      <c r="P19" s="3" t="n">
+        <v/>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2969,13 +2988,12 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2987,7 +3005,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -2998,13 +3016,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -3040,21 +3058,18 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v/>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -3064,7 +3079,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3076,24 +3091,24 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -3105,58 +3120,55 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v/>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3186,12 +3198,13 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>372</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3203,7 +3216,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3217,102 +3230,102 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -3336,7 +3349,8 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3347,65 +3361,66 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v/>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11888
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
@@ -3421,49 +3436,49 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1892
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3496,25 +3511,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3538,32 +3553,36 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">066
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3578,14 +3597,13 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3602,7 +3620,8 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3613,7 +3632,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3631,24 +3650,24 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3657,8 +3676,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3669,7 +3687,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -3678,8 +3696,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7017
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3690,18 +3707,17 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v/>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -3711,55 +3727,54 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">3281
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1731
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>9300407</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3781,55 +3796,47 @@
       <c r="C25" s="3" t="n">
         <v/>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v/>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v/>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v/>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3840,72 +3847,61 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v/>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111561
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v/>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="n">
         <v/>
       </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="V25" s="3" t="n">
+        <v/>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
+          <t xml:space="preserve">4158
+41419
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v/>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -3922,44 +3918,44 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v/>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -3967,25 +3963,23 @@
 </t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="K26" s="3" t="n">
+        <v/>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3997,63 +3991,63 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v/>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4075,132 +4069,135 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">7155
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -4219,18 +4216,21 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -4240,15 +4240,12 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
+      <c r="G28" s="3" t="n">
+        <v/>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4261,95 +4258,95 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
+      <c r="K28" s="3" t="n">
+        <v/>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21610
+</t>
+        </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">9360
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4373,131 +4370,135 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">2150
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">990
 </t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>4343</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4518,16 +4519,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -4539,19 +4543,19 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4560,94 +4564,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
-        <v/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42138
+          <t xml:space="preserve">667
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4667,47 +4676,47 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v/>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -4717,7 +4726,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -4729,55 +4738,59 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v/>
+          <t>99921</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
+</t>
+        </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4132
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -4789,12 +4802,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">81911955
+111
 </t>
         </is>
       </c>
@@ -4815,7 +4829,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0884
+          <t xml:space="preserve">3646
 </t>
         </is>
       </c>
@@ -4827,7 +4841,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 1
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -4839,7 +4853,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4851,22 +4865,22 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">7116
 </t>
         </is>
       </c>
@@ -4878,75 +4892,79 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">2007
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4781
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">19 1 6
+</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
+</t>
+        </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -4967,34 +4985,34 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">4402
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
@@ -5003,96 +5021,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
-        <v/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v/>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5111,12 +5132,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5128,14 +5152,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -5143,45 +5166,48 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v/>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1292
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5190,53 +5216,56 @@
           <t>212</t>
         </is>
       </c>
-      <c r="R34" s="3" t="n">
-        <v/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5255,12 +5284,16 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5271,30 +5304,30 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -5306,22 +5339,23 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452
+</t>
+        </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -5333,48 +5367,45 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v/>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">9868
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5386,7 +5417,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">384
 </t>
         </is>
       </c>
@@ -5410,132 +5441,136 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">665
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1664
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5559,7 +5594,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5571,7 +5606,8 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">422112
+214101
 </t>
         </is>
       </c>
@@ -5581,30 +5617,36 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
-        <v/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455266
+72
+45
+61194929
+</t>
+        </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
@@ -5616,13 +5658,13 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9878
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -5634,13 +5676,13 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5651,16 +5693,21 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t xml:space="preserve">2191
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
@@ -5670,17 +5717,18 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">4225
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5699,131 +5747,135 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
           <t>44841</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
-        <v/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v/>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6813
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
+          <t xml:space="preserve">21372
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v/>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v/>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8792
+</t>
+        </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3809
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5844,12 +5896,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5867,13 +5919,13 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5882,25 +5934,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">777
+141
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5911,53 +5964,53 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">661
+</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5966,15 +6019,12 @@
 </t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v/>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5995,7 +6045,8 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">227
+6443
 </t>
         </is>
       </c>
@@ -6006,13 +6057,13 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -6024,80 +6075,81 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v/>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">789
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -6109,13 +6161,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -6126,7 +6177,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6145,11 +6196,8 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4088
-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v/>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -6159,7 +6207,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6177,7 +6225,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>343</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -6188,75 +6236,73 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1013
-</t>
-        </is>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v/>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
           <t>217</t>
@@ -6270,19 +6316,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6303,13 +6349,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6328,43 +6374,42 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H42" s="3" t="n">
+        <v/>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">56
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -6382,25 +6427,19 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v/>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -6412,7 +6451,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6424,7 +6463,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -6435,7 +6474,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
@@ -6456,144 +6495,135 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">60944
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">7064
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
+          <t xml:space="preserve">7119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v/>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v/>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6614,7 +6644,8 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
+          <t xml:space="preserve">622
+2722208602828
 </t>
         </is>
       </c>
@@ -6626,25 +6657,22 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
+          <t xml:space="preserve">2124
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v/>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -6660,39 +6688,35 @@
 </t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
+      <c r="K44" s="3" t="n">
+        <v/>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550020
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101101101
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6704,55 +6728,43 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10110
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501151000115
-</t>
-        </is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v/>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119898
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
+          <t xml:space="preserve">24222
+7
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v/>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v/>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6777,7 +6789,8 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">672727
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6787,7 +6800,8 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">84
+24222
 </t>
         </is>
       </c>
@@ -6799,21 +6813,18 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v/>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -6823,24 +6834,22 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
+          <t xml:space="preserve">6022
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v/>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6219
+          <t xml:space="preserve">61972
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">6242
 </t>
         </is>
       </c>
@@ -6861,49 +6870,50 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">12089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6923,24 +6933,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6958,50 +6969,45 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">3821
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1044
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -7012,49 +7018,43 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
+          <t xml:space="preserve">929180
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v/>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -685,19 +685,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">71138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -706,108 +706,110 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12668
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -827,24 +829,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
+          <t xml:space="preserve">15643
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -855,18 +857,18 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -878,7 +880,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -888,43 +890,41 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="3" t="n">
-        <v/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v/>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -936,13 +936,12 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -954,14 +953,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -981,20 +979,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1005,27 +1002,30 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01400</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111416
+</t>
+        </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1036,45 +1036,44 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">09942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v/>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">6718
 </t>
         </is>
       </c>
@@ -1086,29 +1085,29 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>120</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11039
 </t>
         </is>
       </c>
@@ -1129,7 +1128,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3552
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1141,129 +1140,118 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2801
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>522</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
+          <t xml:space="preserve">2985
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v/>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1284,136 +1272,136 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3779
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2121
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149712
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127219
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">19178
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -1432,73 +1420,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1825281
+</t>
+        </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v/>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v/>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1513,19 +1502,20 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8929
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t xml:space="preserve">9988
+</t>
         </is>
       </c>
       <c r="U9" s="3" t="n">
@@ -1533,31 +1523,32 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
+          <t xml:space="preserve">194290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1575,47 +1566,44 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3650
+</t>
+        </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v/>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1630,71 +1618,61 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16379
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">430
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v/>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v/>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1706,7 +1684,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -1727,132 +1705,134 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77871
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2531
-228548177
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v/>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v/>
+      <c r="F11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">1107
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v/>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">12895
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">720
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>846</t>
+          <t xml:space="preserve">1186
+</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">1181
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v/>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1871,72 +1851,81 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">5212
+</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277275
-163
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2999
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1947,19 +1936,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2172
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -1971,30 +1960,31 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2015,44 +2005,41 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">94556
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">21138
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2063,35 +2050,38 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t xml:space="preserve">17176
+</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -2101,25 +2091,24 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2131,25 +2120,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2168,81 +2157,81 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203199
+</t>
+        </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3561
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9908
+          <t xml:space="preserve">18202
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979
+          <t xml:space="preserve">9290
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2264,44 +2253,38 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="T14" s="3" t="n">
+        <v/>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065
-</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v/>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -2320,8 +2303,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4845
+</t>
+        </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -2331,37 +2317,34 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">11007
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v/>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3252
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2370,74 +2353,67 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184883
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9226
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
+      <c r="X15" s="3" t="n">
+        <v/>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
@@ -2447,7 +2423,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2468,46 +2444,45 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">23269
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1272
 </t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
-        <v/>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">2957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4236
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">1954819
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v/>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2519,84 +2494,89 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1669
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">194910
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t xml:space="preserve">9290
+</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2614,48 +2594,48 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">2592
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">653
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">11191
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">18241
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2663,28 +2643,30 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v/>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4381
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2694,53 +2676,53 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">5626
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2974
 </t>
         </is>
       </c>
@@ -2759,24 +2741,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3357
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2788,25 +2773,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v/>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2815,80 +2794,78 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
+          <t xml:space="preserve">1940
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v/>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v/>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">27190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2102
+</t>
+        </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">5167
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>6340880</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2908,76 +2885,80 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 85 2
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">111626
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v/>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
       </c>
       <c r="N19" s="3" t="n">
         <v/>
       </c>
-      <c r="O19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2993,36 +2974,34 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v/>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1199
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8948
 </t>
         </is>
       </c>
@@ -3047,80 +3026,76 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">112494
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v/>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v/>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3131,50 +3106,48 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v/>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v/>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3193,50 +3166,56 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3793
+</t>
+        </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11796
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2888
+</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3248,24 +3227,22 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v/>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3277,7 +3254,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3287,47 +3264,38 @@
 </t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
+      <c r="T21" s="3" t="n">
+        <v/>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11694
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v/>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3344,143 +3312,133 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5089
+</t>
+        </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">21132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1295
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2121
-</t>
-        </is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v/>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v/>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v/>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v/>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3499,140 +3457,139 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">11285
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11614
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v/>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">294890
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v/>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">23280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">12198
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>763</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3652,42 +3609,43 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4379 18
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10256
+</t>
+        </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6215659
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v/>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -3696,87 +3654,78 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v/>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v/>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3281
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1731
-</t>
-        </is>
+          <t xml:space="preserve">11894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v/>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>9300407</t>
+          <t xml:space="preserve">188812
+</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v/>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -3793,115 +3742,137 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2336
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28726
+</t>
+        </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1020
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">5189
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="U25" s="3" t="n">
         <v/>
       </c>
-      <c r="V25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v/>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -3918,48 +3889,51 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2583
+</t>
+        </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115178685
-1149791
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3968,84 +3942,87 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">0153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -4064,140 +4041,133 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5358
+</t>
+        </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">12245
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155
+          <t xml:space="preserve">7133
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
+          <t xml:space="preserve">20916
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v/>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v/>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">11835
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v/>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4218,34 +4188,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -4254,99 +4227,93 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21610
-</t>
-        </is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v/>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9360
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v/>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4365,140 +4332,135 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3091
+</t>
+        </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v/>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
+          <t xml:space="preserve">11122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v/>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v/>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8561
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">119910
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4519,54 +4481,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15699
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1168
 </t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">15449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">16294
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1769
 </t>
         </is>
       </c>
@@ -4576,87 +4539,76 @@
 </t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+      <c r="M30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v/>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>4449244</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">667
+          <t xml:space="preserve">94138
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v/>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">9220
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4676,139 +4628,135 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-89191911
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>624</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
+          <t xml:space="preserve">084
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v/>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t xml:space="preserve">859
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4132
+          <t xml:space="preserve">81154
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">1063
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">1 85
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t xml:space="preserve">950
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81911955
-111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4829,144 +4777,120 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646
+          <t xml:space="preserve">3642
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2579
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">128213
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v/>
+      <c r="I32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7116
+          <t xml:space="preserve">7196
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2007
-</t>
-        </is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v/>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4781
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v/>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v/>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 1
-</t>
-        </is>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v/>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4985,135 +4909,132 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4402
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">1132
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">11817
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="I33" s="3" t="n">
+        <v/>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">110972
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">201912
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
         <v/>
       </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
+      <c r="T33" s="3" t="n">
+        <v/>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2916
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">19800
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5134,138 +5055,129 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11452
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1426
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v/>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5286,138 +5198,137 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">1121
+</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">1212818
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9868
-</t>
-        </is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v/>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">384
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5436,141 +5347,137 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6132
+</t>
+        </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">11150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v/>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
+          <t xml:space="preserve">11616
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v/>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5589,147 +5496,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>197824</t>
+        </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422112
-214101
+          <t xml:space="preserve">10922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455266
-72
-45
-61194929
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">16815
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">94920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
-</t>
+          <t>3821914</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2332
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4225
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5749,133 +5651,130 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>44841</t>
-        </is>
+          <t xml:space="preserve">4956
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1741
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1913
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21372
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2190
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8792
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">11720
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1664
+</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+          <t xml:space="preserve">181014
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v/>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">01846
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -5896,36 +5795,37 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">6243
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5934,93 +5834,89 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-141
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v/>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">121202
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v/>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1988
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1628
+</t>
+        </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -6045,25 +5941,25 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-6443
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -6073,66 +5969,66 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v/>
+      <c r="H40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11100
+</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2354
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -6143,41 +6039,42 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">0488
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6196,139 +6093,131 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7943
+</t>
+        </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v/>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1013
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">179
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1726
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">2 1 4
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6355,43 +6244,49 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24709
+</t>
+        </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11605
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6401,23 +6296,17 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
+      <c r="M42" s="3" t="n">
+        <v/>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v/>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -6427,19 +6316,25 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">9490
 </t>
         </is>
       </c>
@@ -6451,30 +6346,31 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6495,88 +6391,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60944
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7064
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v/>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1810
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
-</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
         <v/>
       </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
+      <c r="N43" s="3" t="n">
+        <v/>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6588,19 +6478,19 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6611,19 +6501,19 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">7298
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6642,95 +6532,53 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2124
-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v/>
       </c>
       <c r="F44" s="3" t="n">
         <v/>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
+      <c r="G44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v/>
       </c>
       <c r="K44" s="3" t="n">
         <v/>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
+      <c r="L44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v/>
       </c>
       <c r="S44" s="3" t="n">
         <v/>
@@ -6738,18 +6586,11 @@
       <c r="T44" s="3" t="n">
         <v/>
       </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
+      <c r="U44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v/>
       </c>
       <c r="W44" s="3" t="n">
         <v/>
@@ -6757,11 +6598,8 @@
       <c r="X44" s="3" t="n">
         <v/>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v/>
       </c>
       <c r="Z44" s="3" t="n">
         <v/>
@@ -6789,19 +6627,18 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672727
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">036
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-24222
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6813,106 +6650,113 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11819
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">3564
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
+</t>
+        </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61972
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6242
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v/>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">11263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12089
+          <t xml:space="preserve">11089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">10609
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
+          <t xml:space="preserve">23028 1
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6933,31 +6777,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15034
 </t>
         </is>
       </c>
@@ -6969,13 +6812,13 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3821
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
@@ -6984,79 +6827,75 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">11113
+</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v/>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v/>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929180
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v/>
       </c>
       <c r="Z46" s="3" t="n">
         <v/>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -685,13 +685,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -701,18 +701,21 @@
 </t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
-        <v/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -724,7 +727,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -736,13 +739,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -754,19 +757,20 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">8202
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12668
+          <t xml:space="preserve">8197
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1893
+</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -781,17 +785,21 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
-        <v/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
@@ -803,13 +811,14 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -829,19 +838,20 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15643
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1140
+</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -852,7 +862,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -863,24 +874,25 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -898,21 +910,25 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -936,12 +952,13 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -953,13 +970,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -985,29 +1003,31 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
@@ -1019,30 +1039,31 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09942
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1215621
 </t>
         </is>
       </c>
@@ -1052,8 +1073,11 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="n">
-        <v/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1063,17 +1087,19 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6718
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
@@ -1085,29 +1111,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11039
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1128,7 +1156,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
+          <t xml:space="preserve">2552
 </t>
         </is>
       </c>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -1152,23 +1180,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1180,12 +1210,14 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1196,12 +1228,15 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2985
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
@@ -1211,11 +1246,15 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
@@ -1231,21 +1270,25 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1272,7 +1315,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3778
 </t>
         </is>
       </c>
@@ -1290,49 +1333,55 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149712
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1344,28 +1393,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -1377,13 +1429,13 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19178
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1395,13 +1447,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1422,18 +1474,21 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825281
+          <t xml:space="preserve">18252
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1443,13 +1498,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1461,42 +1516,49 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">12819
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4238
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1508,22 +1570,25 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">9856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9988
-</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">09101
+</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
@@ -1535,19 +1600,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">9498
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194290
+          <t xml:space="preserve">942908
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -1568,7 +1633,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
@@ -1580,20 +1645,27 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1603,28 +1675,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1634,12 +1709,15 @@
 </t>
         </is>
       </c>
-      <c r="P10" s="3" t="n">
-        <v/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83 8
+</t>
+        </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1661,14 +1739,22 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
@@ -1678,13 +1764,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1715,11 +1801,17 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -1729,69 +1821,73 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12895
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1803,13 +1899,13 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -1821,18 +1917,21 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1851,104 +1950,109 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5212
+          <t xml:space="preserve">5811
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2317
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2539
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0800
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1139
 </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2172
-</t>
-        </is>
-      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">141046
 </t>
         </is>
       </c>
@@ -1960,13 +2064,13 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1978,13 +2082,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2005,7 +2109,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94556
+          <t xml:space="preserve">5556
 </t>
         </is>
       </c>
@@ -2017,29 +2121,32 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">2216
+</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21138
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2056,30 +2163,31 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17176
+          <t xml:space="preserve">8196
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2091,7 +2199,8 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2102,15 +2211,12 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v/>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2120,13 +2226,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">078
+          <t xml:space="preserve">1978
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2138,7 +2244,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2159,7 +2265,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203199
+          <t xml:space="preserve">0318
 </t>
         </is>
       </c>
@@ -2171,67 +2277,73 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t xml:space="preserve">2045
+</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18202
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2253,28 +2365,35 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="n">
-        <v/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
@@ -2284,7 +2403,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2317,52 +2436,63 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11007
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2120821
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2372,13 +2502,14 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">2257
+</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -2395,29 +2526,37 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">96480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
@@ -2444,7 +2583,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23269
+          <t xml:space="preserve">230691
 </t>
         </is>
       </c>
@@ -2456,33 +2595,37 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">643
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2957
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954819
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2494,36 +2637,37 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194910
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">11157
 </t>
         </is>
       </c>
@@ -2547,35 +2691,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">558
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t xml:space="preserve">11004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2596,35 +2742,38 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t xml:space="preserve">48141
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18241
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2635,11 +2784,15 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2164
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2649,22 +2802,25 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2676,7 +2832,8 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2687,42 +2844,43 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5626
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2974
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -2743,13 +2901,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2009
 </t>
         </is>
       </c>
@@ -2761,64 +2919,79 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8191
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11822
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9809
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2830,42 +3003,44 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">2106
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">680
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2885,30 +3060,31 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111626
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">11993
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2918,26 +3094,33 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1642
+</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
@@ -2946,7 +3129,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -2958,7 +3141,8 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2969,39 +3153,43 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1794
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">361
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">11995
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -3028,60 +3216,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4949
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112494
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">11958
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
@@ -3095,13 +3291,14 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t xml:space="preserve">1035
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3116,38 +3313,45 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n">
-        <v/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">2588
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3168,48 +3372,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2036
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8916080
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3227,22 +3432,25 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887
+</t>
+        </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">18080
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3260,28 +3468,31 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11694
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -3291,8 +3502,11 @@
 </t>
         </is>
       </c>
-      <c r="Y21" s="3" t="n">
-        <v/>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
       </c>
       <c r="Z21" s="3" t="n">
         <v/>
@@ -3320,103 +3534,112 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>458</t>
+          <t xml:space="preserve">2258
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21132
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
 </t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1046
+</t>
+        </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3428,7 +3651,8 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3437,8 +3661,11 @@
 </t>
         </is>
       </c>
-      <c r="Z22" s="3" t="n">
-        <v/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3469,18 +3696,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11614
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3492,13 +3720,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3510,85 +3738,91 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
+          <t xml:space="preserve">115136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">915
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23280
+          <t xml:space="preserve">3280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">9389
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">11963
 </t>
         </is>
       </c>
@@ -3609,33 +3843,39 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379 18
+          <t xml:space="preserve">49729
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10256
+          <t xml:space="preserve">0256
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6215659
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1234
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1085
+</t>
+        </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3645,16 +3885,20 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">597
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3663,8 +3907,11 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
-        <v/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
@@ -3674,26 +3921,31 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">2919
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3705,16 +3957,19 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1731
+</t>
+        </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188812
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -3724,8 +3979,11 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n">
-        <v/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -3744,93 +4002,97 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
+          <t xml:space="preserve">2536
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">11539
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28726
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">121356
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1962
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3842,35 +4104,43 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1719
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3891,7 +4161,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2583
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
@@ -3903,19 +4173,19 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3933,48 +4203,55 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">888080
+</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3986,13 +4263,13 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4004,25 +4281,25 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4043,42 +4320,45 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5358
+          <t xml:space="preserve">93517
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">013125
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20916
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1117
+</t>
+        </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -4086,44 +4366,52 @@
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
-        <v/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11835
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -4146,7 +4434,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4156,12 +4444,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="3" t="n">
-        <v/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4188,7 +4479,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
@@ -4206,7 +4497,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4218,37 +4509,45 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8075
+</t>
+        </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
@@ -4256,18 +4555,22 @@
 </t>
         </is>
       </c>
-      <c r="P28" s="3" t="n">
-        <v/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -4278,13 +4581,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4296,7 +4599,8 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4346,70 +4650,78 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">20185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4419,12 +4731,15 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="3" t="n">
-        <v/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -4436,31 +4751,31 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119910
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4499,19 +4814,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15449
+          <t xml:space="preserve">6499
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16294
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4523,42 +4838,49 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>4449244</t>
+          <t xml:space="preserve">4910
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">4121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">9989
 </t>
         </is>
       </c>
@@ -4570,45 +4892,50 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94138
+          <t xml:space="preserve">41351
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">8294
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220
+          <t xml:space="preserve">65480
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4634,7 +4961,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4652,30 +4979,33 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4683,22 +5013,24 @@
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n">
-        <v/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
       </c>
       <c r="N31" s="3" t="n">
         <v/>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">14544
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4709,44 +5041,41 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1078
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81154
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">180101
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1063
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 85
-</t>
-        </is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v/>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
@@ -4756,7 +5085,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -4783,61 +5112,66 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128213
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196
+          <t xml:space="preserve">2116
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">751
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4846,7 +5180,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4862,35 +5196,53 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4921,7 +5273,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -4933,50 +5285,55 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">110080
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110972
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">9628
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4988,53 +5345,61 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201912
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2916
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19800
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5055,18 +5420,19 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t xml:space="preserve">2114
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">11972
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11597
 </t>
         </is>
       </c>
@@ -5078,106 +5444,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">003
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">985
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1969
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5204,7 +5585,8 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5215,7 +5597,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">21818
 </t>
         </is>
       </c>
@@ -5233,12 +5615,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -5256,13 +5639,13 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5280,23 +5663,27 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
@@ -5306,29 +5693,31 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5355,42 +5744,43 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">17138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t xml:space="preserve">10995
+</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">11059
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5402,53 +5792,61 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11150
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11616
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5460,24 +5858,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5498,7 +5897,8 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5509,30 +5909,31 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">8194
 </t>
         </is>
       </c>
@@ -5544,76 +5945,79 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">50717
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16815
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3821914</t>
+          <t xml:space="preserve">3809
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">900
+</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -5625,13 +6029,14 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">4299
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5655,87 +6060,98 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
-        <v/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">10251
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">11170
+</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11720
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -5747,34 +6163,37 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181014
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1801
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01846
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -5795,7 +6214,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
+          <t xml:space="preserve">6641
 </t>
         </is>
       </c>
@@ -5807,13 +6226,13 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5825,36 +6244,43 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8 1
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121202
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5866,61 +6292,67 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">15210
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0625
+</t>
+        </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1988
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5947,13 +6379,13 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5965,7 +6397,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5986,13 +6418,13 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -6004,7 +6436,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6016,30 +6448,31 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0488
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
@@ -6051,30 +6484,31 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -6095,7 +6529,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7943
+          <t xml:space="preserve">6943
 </t>
         </is>
       </c>
@@ -6105,119 +6539,135 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
-        <v/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 37
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">01107
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">1053
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12935
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 1 4
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -6238,7 +6688,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -6250,37 +6700,37 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24709
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11605
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6292,21 +6742,27 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -6316,7 +6772,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6328,19 +6784,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
@@ -6352,25 +6808,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6391,19 +6847,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
+          <t xml:space="preserve">6094
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -6412,51 +6868,63 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">16 279
+</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110219
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
@@ -6478,42 +6946,43 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">399
 </t>
         </is>
       </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7298
-</t>
-        </is>
-      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -6532,8 +7001,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="n">
         <v/>
@@ -6627,18 +7099,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">036
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6656,7 +7129,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -6668,13 +7141,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
@@ -6686,77 +7159,79 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t xml:space="preserve">4900
+</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11089
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10609
+          <t xml:space="preserve">6580
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028 1
+          <t xml:space="preserve">3828
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2815
 </t>
         </is>
       </c>
@@ -6783,78 +7258,85 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t xml:space="preserve">11015
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15034
+          <t xml:space="preserve">12004
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111110
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11113
+          <t xml:space="preserve">112198
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1351
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9001
+</t>
+        </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6864,11 +7346,17 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
@@ -6878,15 +7366,12 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
+          <t xml:space="preserve">215416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v/>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
@@ -6894,11 +7379,17 @@
 </t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -739,7 +739,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -751,25 +751,25 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8202
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8197
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -781,7 +781,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -799,7 +799,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -838,7 +838,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
@@ -850,13 +850,13 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -910,7 +910,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -952,13 +952,13 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -976,8 +976,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1003,19 +1002,19 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -1027,7 +1026,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1045,25 +1044,25 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215621
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
@@ -1073,11 +1072,8 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+      <c r="P6" s="3" t="n">
+        <v/>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1123,7 +1119,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1135,7 +1131,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1156,7 +1152,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
@@ -1174,7 +1170,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1210,7 +1206,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1228,7 +1224,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1252,19 +1248,19 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1315,7 +1311,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3778
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
@@ -1327,13 +1323,13 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -1357,7 +1353,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1369,31 +1365,31 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1429,13 +1425,13 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1486,7 +1482,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
@@ -1498,7 +1494,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -1514,15 +1510,12 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
+      <c r="J9" s="3" t="n">
+        <v/>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12819
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1534,31 +1527,31 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4238
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
@@ -1570,13 +1563,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09101
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
@@ -1600,19 +1593,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942908
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1645,7 +1638,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -1657,13 +1650,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -1675,31 +1668,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1711,7 +1704,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83 8
+          <t xml:space="preserve">6 2
 </t>
         </is>
       </c>
@@ -1735,24 +1728,25 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1797,19 +1791,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1839,25 +1833,25 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2 316
 </t>
         </is>
       </c>
@@ -1869,13 +1863,13 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
@@ -1887,7 +1881,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
@@ -1899,31 +1893,31 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1950,7 +1944,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
@@ -1962,7 +1956,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1974,13 +1968,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
@@ -1990,11 +1984,8 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
+      <c r="J12" s="3" t="n">
+        <v/>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -2004,7 +1995,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2016,19 +2007,19 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2040,19 +2031,19 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141046
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2088,7 +2079,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2109,7 +2100,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5556
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
@@ -2121,19 +2112,19 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2163,19 +2154,19 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8196
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2187,7 +2178,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2205,7 +2196,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -2215,8 +2206,11 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="3" t="n">
-        <v/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2220,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2244,7 +2238,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2265,13 +2259,13 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0318
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2289,7 +2283,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2045
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
@@ -2307,13 +2301,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2331,7 +2325,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
@@ -2367,13 +2361,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2385,13 +2379,13 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
@@ -2436,61 +2430,61 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1149
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2120821
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2508,7 +2502,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2526,13 +2520,13 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2544,19 +2538,19 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -2583,7 +2577,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230691
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
@@ -2595,7 +2589,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
@@ -2613,37 +2607,37 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">589
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2655,19 +2649,19 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11157
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2697,7 +2691,7 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11004
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -2709,13 +2703,13 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
@@ -2742,13 +2736,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48141
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2760,13 +2754,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -2784,19 +2778,18 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -2808,13 +2801,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2838,7 +2831,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2880,7 +2873,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2907,7 +2900,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2919,37 +2912,34 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v/>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2961,31 +2951,31 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11822
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9809
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
@@ -3003,31 +2993,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2106
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -3039,7 +3029,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3060,7 +3050,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -3072,13 +3062,13 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11993
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -3102,7 +3092,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3114,22 +3104,25 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3141,7 +3134,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3153,7 +3146,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3165,25 +3158,25 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11995
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -3216,25 +3209,25 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14949
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11958
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -3252,31 +3245,31 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3291,13 +3284,13 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -3309,13 +3302,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3327,13 +3320,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
@@ -3345,7 +3338,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3378,13 +3371,13 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916080
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -3396,19 +3389,19 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3432,7 +3425,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
@@ -3444,7 +3437,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18080
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -3468,7 +3461,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3480,7 +3473,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3492,19 +3485,19 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3534,26 +3527,25 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3568,8 +3560,11 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
-        <v/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -3579,19 +3574,19 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3603,19 +3598,19 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1046
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
@@ -3627,13 +3622,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3651,7 +3646,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3690,7 +3685,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11285
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
@@ -3708,7 +3703,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -3738,19 +3733,19 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
@@ -3760,39 +3755,32 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="P23" s="3" t="n">
+        <v/>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115136
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v/>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
@@ -3804,13 +3792,13 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3822,7 +3810,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11963
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3843,13 +3831,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49729
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0256
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -3873,7 +3861,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1085
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3885,19 +3873,16 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">597
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3909,7 +3894,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3921,19 +3906,19 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2919
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3945,7 +3930,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3963,7 +3948,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3981,7 +3966,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4002,19 +3987,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2536
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11539
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4026,19 +4011,18 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121356
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4050,13 +4034,13 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4068,49 +4052,49 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4122,7 +4106,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4134,13 +4118,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4179,40 +4163,37 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -4221,7 +4202,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4233,19 +4214,19 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888080
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4263,7 +4244,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -4281,19 +4262,19 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
@@ -4320,7 +4301,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93517
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
@@ -4344,19 +4325,19 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">013125
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4374,19 +4355,19 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
@@ -4398,13 +4379,13 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -4420,11 +4401,8 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
+      <c r="T27" s="3" t="n">
+        <v/>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
@@ -4434,7 +4412,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4452,7 +4430,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4479,7 +4457,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
@@ -4497,25 +4475,25 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8075
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -4539,7 +4517,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4581,13 +4559,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4644,27 +4622,24 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20185
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v/>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -4692,7 +4667,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4721,7 +4696,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -4757,13 +4732,13 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4775,7 +4750,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4820,7 +4795,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6499
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
@@ -4838,7 +4813,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4850,37 +4825,34 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4910
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4121
-</t>
-        </is>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v/>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
@@ -4892,13 +4864,13 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41351
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
@@ -4910,31 +4882,31 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8294
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65480
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4967,7 +4939,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -4985,25 +4957,25 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5024,14 +4996,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14544
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v/>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
@@ -5041,7 +5011,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5053,24 +5023,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180101
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5085,7 +5056,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5112,13 +5083,13 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -5136,7 +5107,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5148,35 +5119,38 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">751
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -5192,13 +5166,13 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -5210,13 +5184,13 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -5228,19 +5202,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5273,7 +5247,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
@@ -5285,13 +5259,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110080
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
@@ -5315,19 +5289,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9628
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
@@ -5345,61 +5319,61 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5426,13 +5400,13 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11972
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
@@ -5444,7 +5418,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5462,37 +5436,34 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">003
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v/>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5504,7 +5475,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5522,7 +5493,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -5534,7 +5505,7 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -5546,13 +5517,13 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5579,13 +5550,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5597,13 +5568,13 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21818
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5621,7 +5592,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5643,11 +5614,8 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
+      <c r="N35" s="3" t="n">
+        <v/>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
@@ -5657,25 +5625,25 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5693,7 +5661,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -5705,7 +5673,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5744,19 +5712,19 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10995
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
@@ -5768,13 +5736,13 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11059
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -5792,7 +5760,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5804,25 +5772,25 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5840,19 +5808,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5864,13 +5832,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5933,7 +5901,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -5945,7 +5913,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50717
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
@@ -5957,13 +5925,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5975,7 +5943,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5993,19 +5961,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">38019
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6029,13 +5997,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4299
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6056,14 +6024,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4956
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6074,25 +6041,25 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10251
+          <t xml:space="preserve">10351
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">11702
 </t>
         </is>
       </c>
@@ -6104,7 +6071,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6127,13 +6094,13 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
@@ -6145,13 +6112,13 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -6163,13 +6130,13 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -6187,13 +6154,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6214,7 +6181,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6641
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
@@ -6226,7 +6193,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -6262,13 +6229,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 1
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6280,14 +6246,13 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6298,7 +6263,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6310,25 +6275,25 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15210
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6340,13 +6305,13 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6401,8 +6366,10 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
-        <v/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -6424,13 +6391,13 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6448,13 +6415,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6466,7 +6433,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6484,7 +6451,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6508,7 +6475,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6529,25 +6496,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6943
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
@@ -6557,11 +6524,8 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 37
-</t>
-        </is>
+      <c r="H41" s="3" t="n">
+        <v/>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
@@ -6571,7 +6535,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6583,19 +6547,19 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6613,61 +6577,61 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12935
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">581
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6688,7 +6652,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
@@ -6700,7 +6664,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6712,25 +6676,25 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6742,25 +6706,25 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6772,7 +6736,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -6796,7 +6760,7 @@
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6814,19 +6778,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6847,7 +6811,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">50494
 </t>
         </is>
       </c>
@@ -6868,7 +6832,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 279
+          <t xml:space="preserve">1 279
 </t>
         </is>
       </c>
@@ -6904,25 +6868,25 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110219
+          <t xml:space="preserve">11227
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6946,13 +6910,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6964,25 +6928,25 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -7105,13 +7069,13 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -7135,19 +7099,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -7165,13 +7129,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -7189,20 +7153,19 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7213,25 +7176,25 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3828
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -7264,25 +7227,25 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11015
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12004
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -7300,31 +7263,31 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111110
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112198
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -7342,7 +7305,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -7360,13 +7323,13 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18654
+          <t xml:space="preserve">13654
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215416
+          <t xml:space="preserve">218416
 </t>
         </is>
       </c>
@@ -7381,13 +7344,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -745,7 +745,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -757,13 +757,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -781,7 +781,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -793,7 +793,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">0178
 </t>
         </is>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -838,13 +838,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">4645
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -910,13 +910,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -928,13 +928,13 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -958,7 +958,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -970,13 +970,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1002,37 +1003,37 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1050,19 +1051,19 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1942
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12561
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1089,7 +1090,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1119,19 +1120,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1152,7 +1153,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1224,7 +1225,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1242,7 +1243,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1254,7 +1255,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1266,7 +1267,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1278,7 +1279,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1290,7 +1291,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -1335,7 +1336,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
@@ -1377,13 +1378,13 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1413,7 +1414,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1470,7 +1471,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -1482,8 +1483,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1510,8 +1510,11 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
-        <v/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -1527,25 +1530,25 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1563,13 +1566,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">1986
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">8918
 </t>
         </is>
       </c>
@@ -1581,13 +1584,13 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1599,13 +1602,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1626,7 +1629,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -1650,7 +1653,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1674,25 +1677,25 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -1704,13 +1707,13 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -1728,19 +1731,19 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11914
 </t>
         </is>
       </c>
@@ -1785,25 +1788,25 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">3246
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">753
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -1827,103 +1830,103 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1179
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11228
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2136
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12204
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 316
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1023
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2899
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">11586
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1944,13 +1947,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5111
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -1962,7 +1965,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1974,18 +1977,21 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -1995,55 +2001,55 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2073,13 +2079,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2810
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2100,7 +2106,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
@@ -2112,7 +2118,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
@@ -2124,7 +2130,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2148,25 +2154,25 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2178,7 +2184,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
@@ -2190,19 +2196,18 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">18668
 </t>
         </is>
       </c>
@@ -2232,7 +2237,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
@@ -2259,7 +2264,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -2277,13 +2282,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2313,19 +2318,19 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2337,7 +2342,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2361,13 +2366,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -2379,19 +2384,19 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2418,7 +2423,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">4845
 </t>
         </is>
       </c>
@@ -2442,7 +2447,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2454,19 +2459,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2484,13 +2489,13 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2520,7 +2525,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">652
 </t>
         </is>
       </c>
@@ -2601,7 +2606,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
@@ -2619,13 +2624,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2637,31 +2642,27 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
+          <t xml:space="preserve">4320
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v/>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2685,31 +2686,31 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">2558
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -2736,31 +2737,31 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4614
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">21124
 </t>
         </is>
       </c>
@@ -2778,18 +2779,19 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2807,7 +2809,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2825,7 +2827,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2843,13 +2845,13 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
@@ -2873,7 +2875,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -2894,13 +2896,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
@@ -2924,16 +2926,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2951,19 +2956,19 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9828
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2975,7 +2980,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12168
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -2993,25 +2998,25 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -3062,7 +3067,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
@@ -3074,13 +3079,13 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -3092,13 +3097,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
@@ -3110,20 +3115,19 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3134,7 +3138,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3146,7 +3150,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
@@ -3158,13 +3162,13 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3209,7 +3213,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">14179
 </t>
         </is>
       </c>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">11254
 </t>
         </is>
       </c>
@@ -3273,13 +3277,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="n">
-        <v/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3290,7 +3296,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3308,43 +3314,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">8 0
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3365,7 +3371,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3793
 </t>
         </is>
       </c>
@@ -3377,7 +3383,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">0140
 </t>
         </is>
       </c>
@@ -3389,7 +3395,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3401,7 +3407,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3413,7 +3419,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
@@ -3425,13 +3431,13 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3455,7 +3461,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3473,7 +3479,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -3485,24 +3491,27 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">9181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3533,19 +3542,20 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3580,7 +3590,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3592,43 +3602,43 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">2970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3646,7 +3656,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -3685,7 +3695,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -3703,7 +3713,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -3715,8 +3725,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3727,13 +3736,13 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
@@ -3745,8 +3754,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3755,8 +3763,11 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n">
-        <v/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3777,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">1915
 </t>
         </is>
       </c>
@@ -3775,12 +3786,13 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
@@ -3798,7 +3810,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -3810,7 +3822,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -3831,13 +3843,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">4179
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">0236
 </t>
         </is>
       </c>
@@ -3849,19 +3861,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -3873,7 +3885,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -3882,7 +3894,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3894,7 +3906,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3906,7 +3918,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3930,7 +3942,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -3942,7 +3954,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -3954,7 +3966,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3966,7 +3978,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3987,19 +3999,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">2336
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4011,7 +4023,8 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">76
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -4022,7 +4035,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -4034,25 +4047,25 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4064,13 +4077,13 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4094,37 +4107,36 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4145,7 +4157,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">2283
 </t>
         </is>
       </c>
@@ -4169,13 +4181,13 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4185,8 +4197,11 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
-        <v/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -4208,19 +4223,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4232,19 +4247,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4262,27 +4277,21 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v/>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v/>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4301,7 +4310,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -4325,7 +4334,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">10122
 </t>
         </is>
       </c>
@@ -4337,7 +4346,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4355,19 +4364,19 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4385,7 +4394,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4401,18 +4410,20 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="n">
-        <v/>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4475,7 +4486,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4493,7 +4504,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4517,7 +4528,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4529,7 +4540,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -4553,19 +4564,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4616,7 +4627,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -4628,22 +4639,25 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -4667,7 +4681,8 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1137
+</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4678,19 +4693,18 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4708,13 +4722,13 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4726,19 +4740,19 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -4771,7 +4785,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4795,13 +4809,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4813,19 +4827,19 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">76 9
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
@@ -4837,14 +4851,13 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -4864,7 +4877,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
@@ -4888,25 +4901,25 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">94280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4933,13 +4946,13 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4963,7 +4976,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4973,11 +4986,8 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4987,21 +4997,27 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">604
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001
+</t>
+        </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
@@ -5011,7 +5027,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
@@ -5023,19 +5039,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92116
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">17 0
 </t>
         </is>
       </c>
@@ -5045,8 +5061,11 @@
 </t>
         </is>
       </c>
-      <c r="X31" s="3" t="n">
-        <v/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
@@ -5056,7 +5075,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5083,66 +5102,67 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2207
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">5716
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5160,21 +5180,18 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v/>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
@@ -5182,11 +5199,8 @@
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
+      <c r="U32" s="3" t="n">
+        <v/>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
@@ -5202,19 +5216,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5253,7 +5267,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -5265,19 +5279,19 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5289,19 +5303,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">191619
 </t>
         </is>
       </c>
@@ -5331,49 +5345,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">28809
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5400,13 +5414,13 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5418,13 +5432,13 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5436,13 +5450,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5452,8 +5466,11 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n">
-        <v/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -5463,7 +5480,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5475,7 +5492,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5487,13 +5504,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
@@ -5511,7 +5528,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
@@ -5523,7 +5540,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1900
 </t>
         </is>
       </c>
@@ -5550,25 +5567,25 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
@@ -5580,7 +5597,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5610,12 +5627,15 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
@@ -5625,13 +5645,13 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -5643,13 +5663,13 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1 1 9
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -5661,31 +5681,31 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
@@ -5718,25 +5738,25 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5760,25 +5780,25 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -5790,7 +5810,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5808,13 +5828,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5838,13 +5858,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5871,67 +5891,67 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3523
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">5079
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -5943,7 +5963,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5955,7 +5975,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">599
 </t>
         </is>
       </c>
@@ -5967,7 +5987,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
@@ -5979,7 +5999,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">700
 </t>
         </is>
       </c>
@@ -5997,15 +6017,12 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
+          <t xml:space="preserve">4298
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v/>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -6030,7 +6047,8 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6047,31 +6065,31 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6083,13 +6101,14 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -6100,7 +6119,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -6112,55 +6131,55 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1176
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6181,7 +6200,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">6243
 </t>
         </is>
       </c>
@@ -6193,7 +6212,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6217,24 +6236,25 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -6246,13 +6266,14 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6263,19 +6284,19 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6293,19 +6314,19 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2715
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6317,7 +6338,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -6350,7 +6371,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -6362,13 +6383,14 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -6415,7 +6437,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6433,13 +6455,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
@@ -6451,7 +6473,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6475,7 +6497,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6496,7 +6518,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">6443
 </t>
         </is>
       </c>
@@ -6508,13 +6530,13 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -6527,15 +6549,12 @@
       <c r="H41" s="3" t="n">
         <v/>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
+      <c r="I41" s="3" t="n">
+        <v/>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6547,25 +6566,25 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6583,55 +6602,55 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6664,31 +6683,31 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">4709
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -6700,31 +6719,31 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6736,7 +6755,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6746,42 +6765,39 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">610
@@ -6790,7 +6806,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6811,7 +6827,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
@@ -6823,16 +6839,19 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 279
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6862,91 +6881,90 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91209
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2392
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9720
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -7063,7 +7081,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -7081,7 +7099,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
@@ -7099,43 +7117,42 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1559
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">94980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -7153,19 +7170,20 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7176,19 +7194,19 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">106888
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">23028
 </t>
         </is>
       </c>
@@ -7227,19 +7245,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">11017
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1513
 </t>
         </is>
       </c>
@@ -7257,43 +7275,43 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">111119
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112138
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11019
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0241
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -7305,36 +7323,39 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13654
+          <t xml:space="preserve">0654
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
@@ -7344,13 +7365,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -679,146 +679,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -838,146 +814,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -997,80 +949,67 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -1078,62 +1017,52 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1153,146 +1082,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1312,146 +1217,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1471,14 +1352,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1488,128 +1367,107 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1629,146 +1487,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11914
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1788,146 +1622,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11228
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11586
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1947,146 +1757,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2106,92 +1892,77 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -2201,50 +1972,42 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2264,146 +2027,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2423,146 +2162,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2582,68 +2297,57 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2653,8 +2357,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -2662,62 +2365,52 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2737,146 +2430,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2896,146 +2565,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3055,74 +2700,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3132,68 +2765,57 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3213,74 +2835,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11254
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3290,68 +2900,57 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3371,146 +2970,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3530,146 +3105,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3689,38 +3240,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3730,26 +3275,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3759,26 +3300,22 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
@@ -3786,44 +3323,37 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3843,143 +3373,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0236
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3999,128 +3508,107 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4130,14 +3618,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4157,128 +3643,107 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="3" t="n">
@@ -4286,8 +3751,7 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n">
@@ -4310,110 +3774,92 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10122
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -4423,32 +3869,27 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4468,146 +3909,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4627,68 +4044,57 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -4698,74 +4104,62 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4785,74 +4179,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4865,62 +4247,52 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4940,50 +4312,42 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4991,92 +4355,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 0</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5096,98 +4445,82 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
@@ -5195,8 +4528,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
@@ -5204,32 +4536,27 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5249,146 +4576,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191619
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5408,146 +4711,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5567,146 +4846,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5726,146 +4981,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5885,140 +5116,117 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n">
@@ -6041,146 +5249,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6200,146 +5384,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6359,146 +5519,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6518,32 +5654,27 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
@@ -6554,104 +5685,87 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6671,98 +5785,82 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4709
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
@@ -6770,44 +5868,37 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6827,98 +5918,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -6928,44 +6003,37 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91209
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6985,8 +6053,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -7075,44 +6142,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -7122,98 +6182,82 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7233,146 +6277,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11017
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1513
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111119
-</t>
+          <t>1111111110</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0654
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 0</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>323</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 0</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>06</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1111111110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196404_SF.JPG_pre_QA_QC.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>895</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>301</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>12 0</t>
+          <t>02 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71 2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168 2</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>856</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 04</t>
+          <t>17 00</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1815 0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4490,22 +4490,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 00</t>
+          <t>15 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 1 2 8</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>581</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809 1</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -6192,17 +6192,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
